--- a/corpus/xlsx/level-086/template.xlsx
+++ b/corpus/xlsx/level-086/template.xlsx
@@ -39,25 +39,25 @@
   <!-- fixture padding 6 -->
   <pkg:definedNames>
     <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$40</pkg:definedName>
-    <!-- fixture padding 6 -->
-    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$40</pkg:definedName>
+    <pkg:definedName name="ItemRange1">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange2">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange3">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange4">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange5">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange6">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange7">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange8">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange9">'Report'!$A$40:$D$41</pkg:definedName>
+    <!-- fixture padding 6 -->
+    <pkg:definedName name="ItemRange10">'Report'!$A$40:$D$41</pkg:definedName>
     <!-- fixture padding 6 -->
   </pkg:definedNames>
   <!-- fixture padding 6 -->
@@ -68,7 +68,7 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 6 -->
-<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<pkg:sst xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <!-- fixture padding 6 -->
   <pkg:si>
     <!-- fixture padding 6 -->
@@ -264,6 +264,138 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
@@ -280,6 +412,70 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">us</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">t</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
@@ -296,6 +492,614 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">m</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">r}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">u</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">s</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">p</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">b</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">l</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">i</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
@@ -328,10 +1132,478 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">r</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">l}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">N</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">m</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">Q</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">u</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">n</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">y</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">P</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">r</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">c</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">T</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">o</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">t</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">a</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">l</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
     <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
     <pkg:r>
       <!-- fixture padding 6 -->
       <pkg:rPr>
@@ -360,23 +1632,87 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
+      <pkg:t xml:space="preserve">ms</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">]</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">am</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
     <!-- fixture padding 6 -->
@@ -396,6 +1732,170 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">{d</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">te</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">ms</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">[i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">qu</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">an</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">ti</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">ty}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
@@ -412,6 +1912,154 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">i</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">].</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">pr</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">ic</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">e}</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+  </pkg:si>
+  <!-- fixture padding 6 -->
+  <pkg:si>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
       <pkg:t xml:space="preserve">{</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
@@ -428,1259 +2076,103 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">st</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">m</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">s</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">p</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">b</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">d</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">N</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">m</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">Q</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">n</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">y</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">P</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">T</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">o</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">a</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">l</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">#e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">ac</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">h i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">te</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">ms</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}}{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{n</pkg:t>
+      <pkg:t xml:space="preserve">d.</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">it</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">em</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">s[</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">i+</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">1]</pkg:t>
+      <!-- fixture padding 6 -->
+    </pkg:r>
+    <!-- fixture padding 6 -->
+    <pkg:r>
+      <!-- fixture padding 6 -->
+      <pkg:rPr>
+        <!-- fixture padding 6 -->
+        <pkg:b/>
+        <!-- fixture padding 6 -->
+        <pkg:sz val="11"/>
+        <!-- fixture padding 6 -->
+        <pkg:rFont val="Calibri"/>
+        <!-- fixture padding 6 -->
+      </pkg:rPr>
+      <!-- fixture padding 6 -->
+      <pkg:t xml:space="preserve">.n</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
     <!-- fixture padding 6 -->
@@ -1712,319 +2204,7 @@
         <!-- fixture padding 6 -->
       </pkg:rPr>
       <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e}}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">q</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">u</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">an</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">t</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">y</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-  </pkg:si>
-  <!-- fixture padding 6 -->
-  <pkg:si>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">{</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">p</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">r</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">i</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">c</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">e</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
-      <!-- fixture padding 6 -->
-    </pkg:r>
-    <!-- fixture padding 6 -->
-    <pkg:r>
-      <!-- fixture padding 6 -->
-      <pkg:rPr>
-        <!-- fixture padding 6 -->
-        <pkg:b/>
-        <!-- fixture padding 6 -->
-        <pkg:sz val="11"/>
-        <!-- fixture padding 6 -->
-        <pkg:rFont val="Calibri"/>
-        <!-- fixture padding 6 -->
-      </pkg:rPr>
-      <!-- fixture padding 6 -->
-      <pkg:t xml:space="preserve">}</pkg:t>
+      <pkg:t xml:space="preserve">e}</pkg:t>
       <!-- fixture padding 6 -->
     </pkg:r>
     <!-- fixture padding 6 -->
@@ -3946,7 +4126,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4008,7 +4188,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4070,7 +4250,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4132,7 +4312,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4194,7 +4374,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4256,7 +4436,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4318,7 +4498,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4380,7 +4560,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4442,7 +4622,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4504,7 +4684,7 @@
       <!-- fixture padding 6 -->
       <xdr:nvPicPr>
         <!-- fixture padding 6 -->
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <!-- fixture padding 6 -->
         <xdr:cNvPicPr/>
         <!-- fixture padding 6 -->
@@ -4551,9 +4731,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <!-- fixture padding 6 -->
-<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
-  <!-- fixture padding 6 -->
-  <pkg:autoFilter ref="A39:D40"/>
+<pkg:table xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
+  <!-- fixture padding 6 -->
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 6 -->
   <pkg:tableColumns count="4">
     <!-- fixture padding 6 -->
@@ -4576,7 +4756,7 @@
 <!-- fixture padding 6 -->
 <pkg:worksheet xmlns:pkg="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <!-- fixture padding 6 -->
-  <pkg:dimension ref="A1:J40"/>
+  <pkg:dimension ref="A1:J41"/>
   <!-- fixture padding 6 -->
   <!-- fixture padding 6 -->
   <pkg:sheetFormatPr defaultRowHeight="15"/>
@@ -5231,21 +5411,21 @@
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
-      <pkg:c r="E40" s="0" t="inlineStr">
-        <!-- fixture padding 6 -->
-        <pkg:is>
-          <!-- fixture padding 6 -->
-          <pkg:t xml:space="preserve">{{/each}}</pkg:t>
-          <!-- fixture padding 6 -->
-        </pkg:is>
-        <!-- fixture padding 6 -->
-      </pkg:c>
-      <!-- fixture padding 6 -->
     </pkg:row>
     <!-- fixture padding 6 -->
+    <pkg:row r="41">
+      <!-- fixture padding 6 -->
+      <pkg:c r="A41" s="0" t="s">
+        <!-- fixture padding 6 -->
+        <pkg:v>14</pkg:v>
+        <!-- fixture padding 6 -->
+      </pkg:c>
+      <!-- fixture padding 6 -->
+    </pkg:row>
+    <!-- fixture padding 6 -->
   </pkg:sheetData>
   <!-- fixture padding 6 -->
-  <pkg:autoFilter ref="A39:D40"/>
+  <pkg:autoFilter ref="A39:D41"/>
   <!-- fixture padding 6 -->
   <pkg:mergeCells count="10">
     <!-- fixture padding 6 -->
@@ -5271,7 +5451,7 @@
     <!-- fixture padding 6 -->
   </pkg:mergeCells>
   <!-- fixture padding 6 -->
-  <pkg:conditionalFormatting sqref="B40:B40">
+  <pkg:conditionalFormatting sqref="B40:B41">
     <!-- fixture padding 6 -->
     <pkg:cfRule type="cellIs" priority="1" operator="greaterThan">
       <!-- fixture padding 6 -->
@@ -5283,7 +5463,7 @@
   <!-- fixture padding 6 -->
   <pkg:dataValidations count="8">
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5291,7 +5471,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5299,7 +5479,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="D40:D41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5307,7 +5487,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="E40:E41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5315,7 +5495,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="F40:F41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5323,7 +5503,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="G40:G41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5331,7 +5511,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="H40:H41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5339,7 +5519,7 @@
       <!-- fixture padding 6 -->
     </pkg:dataValidation>
     <!-- fixture padding 6 -->
-    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I40">
+    <pkg:dataValidation type="whole" operator="between" allowBlank="1" sqref="I40:I41">
       <!-- fixture padding 6 -->
       <pkg:formula1>0</pkg:formula1>
       <!-- fixture padding 6 -->
@@ -5374,7 +5554,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>22</pkg:v>
+        <pkg:v>23</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5419,7 +5599,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>23</pkg:v>
+        <pkg:v>24</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5464,7 +5644,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>24</pkg:v>
+        <pkg:v>25</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5509,7 +5689,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>14</pkg:v>
+        <pkg:v>15</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5554,7 +5734,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>15</pkg:v>
+        <pkg:v>16</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5599,7 +5779,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>16</pkg:v>
+        <pkg:v>17</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5644,7 +5824,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>17</pkg:v>
+        <pkg:v>18</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5689,7 +5869,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>18</pkg:v>
+        <pkg:v>19</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5734,7 +5914,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>19</pkg:v>
+        <pkg:v>20</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5779,7 +5959,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>20</pkg:v>
+        <pkg:v>21</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
@@ -5824,7 +6004,7 @@
       <!-- fixture padding 6 -->
       <pkg:c r="A1" s="0" t="s">
         <!-- fixture padding 6 -->
-        <pkg:v>21</pkg:v>
+        <pkg:v>22</pkg:v>
         <!-- fixture padding 6 -->
       </pkg:c>
       <!-- fixture padding 6 -->
